--- a/data/trans_orig/P20-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P20-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2007</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26261</t>
+          <t>26080</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35127</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62692</t>
+          <t>60995</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51308</t>
+          <t>50870</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81850</t>
+          <t>81140</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>666807</t>
+          <t>666988</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>682711</t>
+          <t>682560</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>625659</t>
+          <t>627356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>653224</t>
+          <t>653552</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1299569</t>
+          <t>1300279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1330111</t>
+          <t>1330549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50052</t>
+          <t>49557</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58917</t>
+          <t>58026</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93129</t>
+          <t>92493</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92533</t>
+          <t>92976</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135669</t>
+          <t>136257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>911748</t>
+          <t>912243</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>935570</t>
+          <t>935699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>875264</t>
+          <t>875900</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>909476</t>
+          <t>910367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1794524</t>
+          <t>1793936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1837660</t>
+          <t>1837217</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27641</t>
+          <t>27097</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>52429</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43818</t>
+          <t>44836</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72061</t>
+          <t>74099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78280</t>
+          <t>76454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115388</t>
+          <t>116067</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626139</t>
+          <t>626080</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>650868</t>
+          <t>651412</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>611780</t>
+          <t>609742</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>640023</t>
+          <t>639005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1246962</t>
+          <t>1246283</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1284070</t>
+          <t>1285896</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31982</t>
+          <t>31654</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56724</t>
+          <t>55592</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54920</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87066</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92121</t>
+          <t>92964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135510</t>
+          <t>134465</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>885498</t>
+          <t>886630</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>910240</t>
+          <t>910568</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>951546</t>
+          <t>950541</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>983692</t>
+          <t>983305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1845324</t>
+          <t>1846369</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1888713</t>
+          <t>1887870</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>114463</t>
+          <t>114249</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161027</t>
+          <t>160390</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>221883</t>
+          <t>221283</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>285315</t>
+          <t>281499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>350217</t>
+          <t>347926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>422044</t>
+          <t>424115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3114572</t>
+          <t>3115209</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3161136</t>
+          <t>3161350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3093882</t>
+          <t>3097698</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3157314</t>
+          <t>3157914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6232752</t>
+          <t>6230681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6304579</t>
+          <t>6306870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2012</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2012 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34285</t>
+          <t>34283</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62655</t>
+          <t>61490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60273</t>
+          <t>58913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94349</t>
+          <t>93372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102505</t>
+          <t>104367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>146358</t>
+          <t>144783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>640814</t>
+          <t>641979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>669184</t>
+          <t>669186</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>602701</t>
+          <t>603678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>636777</t>
+          <t>638137</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1254161</t>
+          <t>1255736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1298014</t>
+          <t>1296152</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47760</t>
+          <t>46906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78258</t>
+          <t>79275</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,47 +3038,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>96332</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>79340</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>115913</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>7,69%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>96332</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>78287</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>115838</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>134886</t>
+          <t>134763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182916</t>
+          <t>185848</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>939689</t>
+          <t>938672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>970187</t>
+          <t>971041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,49 +3151,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>92,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>935852</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>916271</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>952844</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>90,67%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>88,77%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>92,31%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>935852</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>916346</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>953897</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,67%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>88,78%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>92,42%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1732</t>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1867215</t>
+          <t>1864283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1915245</t>
+          <t>1915368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35109</t>
+          <t>34574</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64652</t>
+          <t>64471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60459</t>
+          <t>59615</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93135</t>
+          <t>94481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102181</t>
+          <t>102749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147485</t>
+          <t>148191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>690924</t>
+          <t>691105</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>720467</t>
+          <t>721002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>684039</t>
+          <t>682693</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>716715</t>
+          <t>717559</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1385265</t>
+          <t>1384559</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1430569</t>
+          <t>1430001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40862</t>
+          <t>39942</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69324</t>
+          <t>69682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73803</t>
+          <t>73562</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111313</t>
+          <t>109409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119980</t>
+          <t>122898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168014</t>
+          <t>168006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>878415</t>
+          <t>878057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>906877</t>
+          <t>907797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>940588</t>
+          <t>942492</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>978098</t>
+          <t>978339</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1831626</t>
+          <t>1831634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1879660</t>
+          <t>1876742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181142</t>
+          <t>179576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>240563</t>
+          <t>238955</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>304031</t>
+          <t>305250</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>374818</t>
+          <t>377915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>501689</t>
+          <t>498597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>591963</t>
+          <t>594004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3184168</t>
+          <t>3185776</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3243589</t>
+          <t>3245155</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3183491</t>
+          <t>3180394</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3254278</t>
+          <t>3253059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6391077</t>
+          <t>6389036</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6481351</t>
+          <t>6484443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2016</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26172</t>
+          <t>24676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48732</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33576</t>
+          <t>33892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61082</t>
+          <t>60019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65260</t>
+          <t>65754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101901</t>
+          <t>102852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>626068</t>
+          <t>625047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>648628</t>
+          <t>650124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>611757</t>
+          <t>612820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>639263</t>
+          <t>638947</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1245738</t>
+          <t>1244787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1282379</t>
+          <t>1281885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>33220</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60424</t>
+          <t>60873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60929</t>
+          <t>59984</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97423</t>
+          <t>96974</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104791</t>
+          <t>102133</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148908</t>
+          <t>145823</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>962007</t>
+          <t>961558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>988941</t>
+          <t>989211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>945490</t>
+          <t>945939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>981984</t>
+          <t>982929</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1916436</t>
+          <t>1919521</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1960553</t>
+          <t>1963211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>22087</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>48638</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42892</t>
+          <t>42052</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72284</t>
+          <t>72051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71162</t>
+          <t>71823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109559</t>
+          <t>109267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>712216</t>
+          <t>710914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>737684</t>
+          <t>737465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>712727</t>
+          <t>712960</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>742119</t>
+          <t>742959</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1435004</t>
+          <t>1435296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1473401</t>
+          <t>1472740</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36867</t>
+          <t>36686</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64331</t>
+          <t>63144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77631</t>
+          <t>76800</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116328</t>
+          <t>115393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118667</t>
+          <t>121240</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167448</t>
+          <t>168424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>873236</t>
+          <t>874423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>900700</t>
+          <t>900881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>927451</t>
+          <t>928386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>966148</t>
+          <t>966979</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1813898</t>
+          <t>1812922</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1862679</t>
+          <t>1860106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>138465</t>
+          <t>138742</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190218</t>
+          <t>189650</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>241903</t>
+          <t>242355</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>306475</t>
+          <t>309016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>396890</t>
+          <t>396945</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>477952</t>
+          <t>480834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3204132</t>
+          <t>3204700</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3255885</t>
+          <t>3255608</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3238067</t>
+          <t>3235526</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3302639</t>
+          <t>3302187</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6460940</t>
+          <t>6458058</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6542002</t>
+          <t>6541947</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2023</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2023 (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33347</t>
+          <t>33200</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59076</t>
+          <t>58740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32031</t>
+          <t>32890</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>55852</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71682</t>
+          <t>70813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105711</t>
+          <t>103926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>576365</t>
+          <t>576701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>602094</t>
+          <t>602241</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>622076</t>
+          <t>619900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>643721</t>
+          <t>642862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1205483</t>
+          <t>1207268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1239512</t>
+          <t>1240381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>24193</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67555</t>
+          <t>70284</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50220</t>
+          <t>49476</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79375</t>
+          <t>80533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72875</t>
+          <t>71728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137663</t>
+          <t>137466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1125309</t>
+          <t>1122580</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1166922</t>
+          <t>1168671</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>878731</t>
+          <t>877573</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>907886</t>
+          <t>908630</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2013308</t>
+          <t>2013505</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2078096</t>
+          <t>2079243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24820</t>
+          <t>25456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48114</t>
+          <t>49316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>18507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55799</t>
+          <t>55650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47640</t>
+          <t>47816</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93306</t>
+          <t>94017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656566</t>
+          <t>655364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679860</t>
+          <t>679224</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>877567</t>
+          <t>877716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>913208</t>
+          <t>914859</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1544740</t>
+          <t>1544029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1590406</t>
+          <t>1590230</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48034</t>
+          <t>47816</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77560</t>
+          <t>75086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56585</t>
+          <t>55568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88699</t>
+          <t>87963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111543</t>
+          <t>110584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154224</t>
+          <t>154075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>849271</t>
+          <t>851745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>878797</t>
+          <t>879015</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1003894</t>
+          <t>1004630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1036008</t>
+          <t>1037025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1865200</t>
+          <t>1865349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907881</t>
+          <t>1908840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148604</t>
+          <t>147065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>219461</t>
+          <t>219115</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>177874</t>
+          <t>175872</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>249496</t>
+          <t>249986</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,47 +7996,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>404902</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>346082</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>448675</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>4,86%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>404902</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>348675</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>450091</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3240356</t>
+          <t>3240702</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3311213</t>
+          <t>3312752</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3410321</t>
+          <t>3409831</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3481943</t>
+          <t>3483945</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,47 +8109,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>8167</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6714732</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6670959</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6773552</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>94,31%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>93,7%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>95,14%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>8167</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6714732</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6669543</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6770959</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>94,31%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>93,68%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P20-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26080</t>
+          <t>26161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34799</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60995</t>
+          <t>63149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50870</t>
+          <t>51755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81140</t>
+          <t>81721</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>666988</t>
+          <t>666907</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>682560</t>
+          <t>682556</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>627356</t>
+          <t>625202</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>653552</t>
+          <t>652065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1300279</t>
+          <t>1299698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1330549</t>
+          <t>1329664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26101</t>
+          <t>26860</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49557</t>
+          <t>50946</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58026</t>
+          <t>58854</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92493</t>
+          <t>93351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92976</t>
+          <t>93141</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136257</t>
+          <t>136362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>912243</t>
+          <t>910854</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>935699</t>
+          <t>934940</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>875900</t>
+          <t>875042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>910367</t>
+          <t>909539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1793936</t>
+          <t>1793831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1837217</t>
+          <t>1837052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27097</t>
+          <t>27621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52429</t>
+          <t>52824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44836</t>
+          <t>44255</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74099</t>
+          <t>71953</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76454</t>
+          <t>79760</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116067</t>
+          <t>117231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626080</t>
+          <t>625685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651412</t>
+          <t>650888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>609742</t>
+          <t>611888</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>639005</t>
+          <t>639586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1246283</t>
+          <t>1245119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1285896</t>
+          <t>1282590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31654</t>
+          <t>32268</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55592</t>
+          <t>56735</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>53825</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>87041</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92964</t>
+          <t>91928</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134465</t>
+          <t>134668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>886630</t>
+          <t>885487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>910568</t>
+          <t>909954</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>950541</t>
+          <t>951571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>983305</t>
+          <t>984787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1846369</t>
+          <t>1846166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1887870</t>
+          <t>1888906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>114249</t>
+          <t>113852</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160390</t>
+          <t>161439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>221283</t>
+          <t>217521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>281499</t>
+          <t>281291</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>347926</t>
+          <t>345434</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>424115</t>
+          <t>423699</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3115209</t>
+          <t>3114160</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3161350</t>
+          <t>3161747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3097698</t>
+          <t>3097906</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3157914</t>
+          <t>3161676</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6230681</t>
+          <t>6231097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6306870</t>
+          <t>6309362</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34283</t>
+          <t>34117</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61490</t>
+          <t>60842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58913</t>
+          <t>60651</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93372</t>
+          <t>94171</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104367</t>
+          <t>100370</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144783</t>
+          <t>143540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>641979</t>
+          <t>642627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>669186</t>
+          <t>669352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>603678</t>
+          <t>602879</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>638137</t>
+          <t>636399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1255736</t>
+          <t>1256979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1296152</t>
+          <t>1300149</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46906</t>
+          <t>47622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79275</t>
+          <t>78364</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79340</t>
+          <t>77042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115913</t>
+          <t>116147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>134763</t>
+          <t>132737</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>185848</t>
+          <t>182559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>938672</t>
+          <t>939583</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>971041</t>
+          <t>970325</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>916271</t>
+          <t>916037</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>952844</t>
+          <t>955142</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1864283</t>
+          <t>1867572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1915368</t>
+          <t>1917394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34574</t>
+          <t>34456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64471</t>
+          <t>65557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59615</t>
+          <t>60229</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94481</t>
+          <t>93445</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102749</t>
+          <t>101117</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>148191</t>
+          <t>147426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>691105</t>
+          <t>690019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>721002</t>
+          <t>721120</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>682693</t>
+          <t>683729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>717559</t>
+          <t>716945</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1384559</t>
+          <t>1385324</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1430001</t>
+          <t>1431633</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39942</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69682</t>
+          <t>69253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73562</t>
+          <t>73153</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109409</t>
+          <t>109642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122898</t>
+          <t>121625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168006</t>
+          <t>166001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>878057</t>
+          <t>878486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>907797</t>
+          <t>908342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>942492</t>
+          <t>942259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>978339</t>
+          <t>978748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1831634</t>
+          <t>1833639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1876742</t>
+          <t>1878015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>179576</t>
+          <t>182917</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>238955</t>
+          <t>241405</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>305250</t>
+          <t>304653</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>377915</t>
+          <t>372775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>498597</t>
+          <t>501056</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>594004</t>
+          <t>597539</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3185776</t>
+          <t>3183326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3245155</t>
+          <t>3241814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3180394</t>
+          <t>3185534</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3253059</t>
+          <t>3253656</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6389036</t>
+          <t>6385501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6484443</t>
+          <t>6481984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24676</t>
+          <t>25552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49753</t>
+          <t>49002</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33892</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60019</t>
+          <t>60038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65754</t>
+          <t>67742</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102852</t>
+          <t>104808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>625047</t>
+          <t>625798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>650124</t>
+          <t>649248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>612820</t>
+          <t>612801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>638947</t>
+          <t>639302</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1244787</t>
+          <t>1242831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1281885</t>
+          <t>1279897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33220</t>
+          <t>32963</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60873</t>
+          <t>61235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59984</t>
+          <t>59835</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96974</t>
+          <t>95736</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102133</t>
+          <t>101355</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145823</t>
+          <t>147420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>961558</t>
+          <t>961196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>989211</t>
+          <t>989468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>945939</t>
+          <t>947177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>982929</t>
+          <t>983078</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1919521</t>
+          <t>1917924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1963211</t>
+          <t>1963989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22087</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48638</t>
+          <t>47645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42052</t>
+          <t>43416</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72051</t>
+          <t>73080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71823</t>
+          <t>70761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109267</t>
+          <t>108577</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>710914</t>
+          <t>711907</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>737465</t>
+          <t>737604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>712960</t>
+          <t>711931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>742959</t>
+          <t>741595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1435296</t>
+          <t>1435986</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1472740</t>
+          <t>1473802</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36686</t>
+          <t>35889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63144</t>
+          <t>63795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76800</t>
+          <t>76266</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115393</t>
+          <t>114587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121240</t>
+          <t>120305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168424</t>
+          <t>169144</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>874423</t>
+          <t>873772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>900881</t>
+          <t>901678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>928386</t>
+          <t>929192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>966979</t>
+          <t>967513</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1812922</t>
+          <t>1812202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1860106</t>
+          <t>1861041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>138742</t>
+          <t>140882</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189650</t>
+          <t>189532</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>242355</t>
+          <t>243318</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>309016</t>
+          <t>308758</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>396945</t>
+          <t>395829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>480834</t>
+          <t>484261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3204700</t>
+          <t>3204818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3255608</t>
+          <t>3253468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3235526</t>
+          <t>3235784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3302187</t>
+          <t>3301224</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6458058</t>
+          <t>6454631</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6541947</t>
+          <t>6543063</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44350</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33200</t>
+          <t>35922</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58740</t>
+          <t>61735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,27 +6604,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42197</t>
+          <t>46899</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>36486</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55852</t>
+          <t>60650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>86547</t>
+          <t>94819</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70813</t>
+          <t>78699</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103926</t>
+          <t>114878</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>591091</t>
+          <t>642789</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>576701</t>
+          <t>628975</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>602241</t>
+          <t>654788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,22 +6717,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>633555</t>
+          <t>686214</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>619900</t>
+          <t>672463</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>642862</t>
+          <t>696627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1224647</t>
+          <t>1329004</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1207268</t>
+          <t>1308945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1240381</t>
+          <t>1345124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47488</t>
+          <t>54618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24193</t>
+          <t>40316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70284</t>
+          <t>73623</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63352</t>
+          <t>69711</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49476</t>
+          <t>55629</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80533</t>
+          <t>89167</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>110840</t>
+          <t>124329</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71728</t>
+          <t>105999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137466</t>
+          <t>152173</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1145376</t>
+          <t>994299</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1122580</t>
+          <t>975294</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1168671</t>
+          <t>1008601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>894754</t>
+          <t>1001127</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>877573</t>
+          <t>981671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>908630</t>
+          <t>1015209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2040131</t>
+          <t>1995426</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2013505</t>
+          <t>1967582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2079243</t>
+          <t>2013756</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38042</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25456</t>
+          <t>27006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49316</t>
+          <t>50523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>49748</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>37698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55650</t>
+          <t>65796</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>74217</t>
+          <t>87790</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47816</t>
+          <t>71700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94017</t>
+          <t>107208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>669291</t>
+          <t>765031</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655364</t>
+          <t>752550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679224</t>
+          <t>776067</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>894538</t>
+          <t>762511</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>877716</t>
+          <t>746463</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>914859</t>
+          <t>774561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1563829</t>
+          <t>1527542</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1544029</t>
+          <t>1508124</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1590230</t>
+          <t>1543632</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60831</t>
+          <t>64598</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47816</t>
+          <t>51406</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75086</t>
+          <t>80486</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>72467</t>
+          <t>79110</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55568</t>
+          <t>64448</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87963</t>
+          <t>94246</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>133298</t>
+          <t>143708</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110584</t>
+          <t>123709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154075</t>
+          <t>165006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>866000</t>
+          <t>925464</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>851745</t>
+          <t>909576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879015</t>
+          <t>938656</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1020126</t>
+          <t>1039209</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1004630</t>
+          <t>1024073</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1037025</t>
+          <t>1053871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1886126</t>
+          <t>1964673</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1865349</t>
+          <t>1943375</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1908840</t>
+          <t>1984672</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147065</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>219115</t>
+          <t>233033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>175872</t>
+          <t>218887</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>249986</t>
+          <t>275599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>346082</t>
+          <t>411442</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>448675</t>
+          <t>487883</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3271759</t>
+          <t>3327584</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3240702</t>
+          <t>3299729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3312752</t>
+          <t>3353630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3442974</t>
+          <t>3489062</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3409831</t>
+          <t>3458930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3483945</t>
+          <t>3515642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6714732</t>
+          <t>6816646</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6670959</t>
+          <t>6779408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6773552</t>
+          <t>6855849</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3659817</t>
+          <t>3734529</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3659817</t>
+          <t>3734529</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3659817</t>
+          <t>3734529</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7119634</t>
+          <t>7267291</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7119634</t>
+          <t>7267291</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7119634</t>
+          <t>7267291</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
